--- a/INFANTIL.xlsx
+++ b/INFANTIL.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="HTML_1" vbProcedure="false">Planilha1!$A$1:$T$342</definedName>
-    <definedName function="false" hidden="false" name="HTML_all" vbProcedure="false">Planilha1!$A$1:$T$342</definedName>
+    <definedName function="false" hidden="false" name="HTML_1" vbProcedure="false">Planilha1!$A$1:$T$343</definedName>
+    <definedName function="false" hidden="false" name="HTML_all" vbProcedure="false">Planilha1!$A$1:$T$343</definedName>
     <definedName function="false" hidden="false" name="HTML_tables" vbProcedure="false">#REF!</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3502" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="992">
   <si>
     <t xml:space="preserve">Nº classe</t>
   </si>
@@ -804,7 +804,7 @@
     <t xml:space="preserve">29/11/2021</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA JOSÉ CABANILLES - 130, FAZENDA DA JUTA - SAO PAULO - SP</t>
+    <t xml:space="preserve">RUA JOSÉ CABANILLES - 75, FAZENDA DA JUTA - SAO PAULO - SP</t>
   </si>
   <si>
     <t xml:space="preserve">PEDRO RODRIGUES MOURA</t>
@@ -2241,7 +2241,7 @@
     <t xml:space="preserve">RUA ROSETA - 84, PARQUE CAPUAVA - SANTO ANDRE - SP</t>
   </si>
   <si>
-    <t xml:space="preserve">KAUA LEVI CAMPOS FELIX</t>
+    <t xml:space="preserve">KAUA LEVI CAMPOS</t>
   </si>
   <si>
     <t xml:space="preserve">05/03/2021</t>
@@ -2250,7 +2250,7 @@
     <t xml:space="preserve">15/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">RUA ASA BRANCA - 281, JARDIM ALZIRA FRANCO - SANTO ANDRE - SP</t>
+    <t xml:space="preserve">RUA CLENIO WANDERLEY - 25, FAZENDA DA JUTA - SAO PAULO - SP</t>
   </si>
   <si>
     <t xml:space="preserve">LEONARDO GONCALVES RODRIGUES</t>
@@ -2568,6 +2568,9 @@
     <t xml:space="preserve">10/03/2021</t>
   </si>
   <si>
+    <t xml:space="preserve">TRAN</t>
+  </si>
+  <si>
     <t xml:space="preserve">RUA NEPAL - 142, PARQUE CAPUAVA - SANTO ANDRE - SP</t>
   </si>
   <si>
@@ -2668,6 +2671,9 @@
   </si>
   <si>
     <t xml:space="preserve">RUA SAQUAREMA - 185, PARQUE JOÃO RAMALHO - SANTO ANDRE - SP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">BENJAMIM SOARES DE SOUZA</t>
@@ -3210,8 +3216,30 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T342"/>
+  <dimension ref="A1:T343"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="51.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="91.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="12.56"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -18024,7 +18052,7 @@
         <v>419</v>
       </c>
       <c r="L284" s="1" t="s">
-        <v>775</v>
+        <v>847</v>
       </c>
       <c r="M284" s="2" t="s">
         <v>419</v>
@@ -18035,7 +18063,7 @@
       <c r="Q284" s="1"/>
       <c r="R284" s="1"/>
       <c r="S284" s="1" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="T284" s="1" t="s">
         <v>29</v>
@@ -18073,13 +18101,13 @@
         <v>24</v>
       </c>
       <c r="K285" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L285" s="1" t="s">
         <v>51</v>
       </c>
       <c r="M285" s="2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
@@ -18107,7 +18135,7 @@
         <v>10</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F286" s="1" t="n">
         <v>122632772</v>
@@ -18119,7 +18147,7 @@
         <v>22</v>
       </c>
       <c r="I286" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>24</v>
@@ -18139,7 +18167,7 @@
       <c r="Q286" s="1"/>
       <c r="R286" s="1"/>
       <c r="S286" s="1" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="T286" s="1" t="s">
         <v>29</v>
@@ -18159,7 +18187,7 @@
         <v>11</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F287" s="1" t="n">
         <v>123398246</v>
@@ -18171,7 +18199,7 @@
         <v>22</v>
       </c>
       <c r="I287" s="2" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>24</v>
@@ -18191,7 +18219,7 @@
       <c r="Q287" s="1"/>
       <c r="R287" s="1"/>
       <c r="S287" s="1" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="T287" s="1" t="s">
         <v>29</v>
@@ -18211,7 +18239,7 @@
         <v>12</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F288" s="1" t="n">
         <v>123834241</v>
@@ -18223,7 +18251,7 @@
         <v>22</v>
       </c>
       <c r="I288" s="2" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>24</v>
@@ -18243,7 +18271,7 @@
       <c r="Q288" s="1"/>
       <c r="R288" s="1"/>
       <c r="S288" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="T288" s="1" t="s">
         <v>29</v>
@@ -18263,7 +18291,7 @@
         <v>13</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F289" s="1" t="n">
         <v>122918431</v>
@@ -18295,7 +18323,7 @@
       <c r="Q289" s="1"/>
       <c r="R289" s="1"/>
       <c r="S289" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="T289" s="1" t="s">
         <v>29</v>
@@ -18315,7 +18343,7 @@
         <v>14</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F290" s="1" t="n">
         <v>123655707</v>
@@ -18327,7 +18355,7 @@
         <v>22</v>
       </c>
       <c r="I290" s="2" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="J290" s="2" t="s">
         <v>24</v>
@@ -18347,7 +18375,7 @@
       <c r="Q290" s="1"/>
       <c r="R290" s="1"/>
       <c r="S290" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="T290" s="1" t="s">
         <v>29</v>
@@ -18367,7 +18395,7 @@
         <v>15</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="F291" s="1" t="n">
         <v>123222452</v>
@@ -18379,7 +18407,7 @@
         <v>22</v>
       </c>
       <c r="I291" s="2" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="J291" s="2" t="s">
         <v>24</v>
@@ -18399,7 +18427,7 @@
       <c r="Q291" s="1"/>
       <c r="R291" s="1"/>
       <c r="S291" s="1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="T291" s="1" t="s">
         <v>29</v>
@@ -18419,7 +18447,7 @@
         <v>16</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F292" s="1" t="n">
         <v>124193223</v>
@@ -18451,7 +18479,7 @@
       <c r="Q292" s="1"/>
       <c r="R292" s="1"/>
       <c r="S292" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="T292" s="1" t="s">
         <v>29</v>
@@ -18523,7 +18551,7 @@
         <v>18</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="F294" s="1" t="n">
         <v>123546975</v>
@@ -18535,7 +18563,7 @@
         <v>22</v>
       </c>
       <c r="I294" s="2" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>24</v>
@@ -18555,7 +18583,7 @@
       <c r="Q294" s="1"/>
       <c r="R294" s="1"/>
       <c r="S294" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="T294" s="1" t="s">
         <v>29</v>
@@ -18575,7 +18603,7 @@
         <v>19</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F295" s="1" t="n">
         <v>124193330</v>
@@ -18607,7 +18635,7 @@
       <c r="Q295" s="1"/>
       <c r="R295" s="1"/>
       <c r="S295" s="1" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="T295" s="1" t="s">
         <v>29</v>
@@ -18627,7 +18655,7 @@
         <v>20</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="F296" s="1" t="n">
         <v>123265546</v>
@@ -18659,7 +18687,7 @@
       <c r="Q296" s="1"/>
       <c r="R296" s="1"/>
       <c r="S296" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="T296" s="1" t="s">
         <v>29</v>
@@ -18679,7 +18707,7 @@
         <v>21</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F297" s="1" t="n">
         <v>123258144</v>
@@ -18691,7 +18719,7 @@
         <v>22</v>
       </c>
       <c r="I297" s="2" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>24</v>
@@ -18711,7 +18739,7 @@
       <c r="Q297" s="1"/>
       <c r="R297" s="1"/>
       <c r="S297" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="T297" s="1" t="s">
         <v>29</v>
@@ -18731,7 +18759,7 @@
         <v>22</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F298" s="1" t="n">
         <v>122427661</v>
@@ -18743,7 +18771,7 @@
         <v>22</v>
       </c>
       <c r="I298" s="2" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>24</v>
@@ -18763,7 +18791,7 @@
       <c r="Q298" s="1"/>
       <c r="R298" s="1"/>
       <c r="S298" s="1" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="T298" s="1" t="s">
         <v>29</v>
@@ -18823,7 +18851,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="n">
-        <v>300558944</v>
+        <v>300558929</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>20</v>
@@ -18832,25 +18860,25 @@
         <v>2</v>
       </c>
       <c r="D300" s="1" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>881</v>
+        <v>845</v>
       </c>
       <c r="F300" s="1" t="n">
-        <v>123264873</v>
+        <v>126256987</v>
       </c>
       <c r="G300" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H300" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I300" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="J300" s="2" t="s">
         <v>882</v>
-      </c>
-      <c r="J300" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="K300" s="2" t="s">
         <v>25</v>
@@ -18867,7 +18895,7 @@
       <c r="Q300" s="1"/>
       <c r="R300" s="1"/>
       <c r="S300" s="1" t="s">
-        <v>883</v>
+        <v>848</v>
       </c>
       <c r="T300" s="1" t="s">
         <v>29</v>
@@ -18884,13 +18912,13 @@
         <v>2</v>
       </c>
       <c r="D301" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F301" s="1" t="n">
-        <v>124386580</v>
+        <v>123264873</v>
       </c>
       <c r="G301" s="1" t="n">
         <v>5</v>
@@ -18899,7 +18927,7 @@
         <v>22</v>
       </c>
       <c r="I301" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>24</v>
@@ -18913,15 +18941,13 @@
       <c r="M301" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N301" s="1" t="s">
-        <v>85</v>
-      </c>
+      <c r="N301" s="1"/>
       <c r="O301" s="1"/>
       <c r="P301" s="1"/>
       <c r="Q301" s="1"/>
       <c r="R301" s="1"/>
       <c r="S301" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="T301" s="1" t="s">
         <v>29</v>
@@ -18938,23 +18964,23 @@
         <v>2</v>
       </c>
       <c r="D302" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E302" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="F302" s="1" t="n">
+        <v>124386580</v>
+      </c>
+      <c r="G302" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H302" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I302" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="F302" s="1" t="n">
-        <v>123247986</v>
-      </c>
-      <c r="G302" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H302" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I302" s="2" t="s">
-        <v>888</v>
-      </c>
       <c r="J302" s="2" t="s">
         <v>24</v>
       </c>
@@ -18967,13 +18993,15 @@
       <c r="M302" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N302" s="1"/>
+      <c r="N302" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="O302" s="1"/>
       <c r="P302" s="1"/>
       <c r="Q302" s="1"/>
       <c r="R302" s="1"/>
       <c r="S302" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="T302" s="1" t="s">
         <v>29</v>
@@ -18990,34 +19018,34 @@
         <v>2</v>
       </c>
       <c r="D303" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E303" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="F303" s="1" t="n">
+        <v>123247986</v>
+      </c>
+      <c r="G303" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H303" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I303" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="F303" s="1" t="n">
-        <v>124206991</v>
-      </c>
-      <c r="G303" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H303" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I303" s="2" t="s">
-        <v>891</v>
-      </c>
       <c r="J303" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K303" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L303" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M303" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="M303" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
@@ -19025,7 +19053,7 @@
       <c r="Q303" s="1"/>
       <c r="R303" s="1"/>
       <c r="S303" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="T303" s="1" t="s">
         <v>29</v>
@@ -19042,34 +19070,34 @@
         <v>2</v>
       </c>
       <c r="D304" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E304" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="F304" s="1" t="n">
+        <v>124206991</v>
+      </c>
+      <c r="G304" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H304" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I304" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="F304" s="1" t="n">
-        <v>124260445</v>
-      </c>
-      <c r="G304" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H304" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I304" s="2" t="s">
-        <v>894</v>
-      </c>
       <c r="J304" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K304" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L304" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M304" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
+      </c>
+      <c r="M304" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
@@ -19077,7 +19105,7 @@
       <c r="Q304" s="1"/>
       <c r="R304" s="1"/>
       <c r="S304" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="T304" s="1" t="s">
         <v>29</v>
@@ -19094,23 +19122,23 @@
         <v>2</v>
       </c>
       <c r="D305" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E305" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F305" s="1" t="n">
+        <v>124260445</v>
+      </c>
+      <c r="G305" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H305" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I305" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="F305" s="1" t="n">
-        <v>123314046</v>
-      </c>
-      <c r="G305" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H305" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I305" s="2" t="s">
-        <v>897</v>
-      </c>
       <c r="J305" s="2" t="s">
         <v>24</v>
       </c>
@@ -19123,15 +19151,13 @@
       <c r="M305" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N305" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="N305" s="1"/>
       <c r="O305" s="1"/>
       <c r="P305" s="1"/>
       <c r="Q305" s="1"/>
       <c r="R305" s="1"/>
       <c r="S305" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="T305" s="1" t="s">
         <v>29</v>
@@ -19148,23 +19174,23 @@
         <v>2</v>
       </c>
       <c r="D306" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E306" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="F306" s="1" t="n">
+        <v>123314046</v>
+      </c>
+      <c r="G306" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I306" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="F306" s="1" t="n">
-        <v>124520438</v>
-      </c>
-      <c r="G306" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H306" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I306" s="2" t="s">
-        <v>900</v>
-      </c>
       <c r="J306" s="2" t="s">
         <v>24</v>
       </c>
@@ -19177,13 +19203,15 @@
       <c r="M306" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N306" s="1"/>
+      <c r="N306" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="O306" s="1"/>
       <c r="P306" s="1"/>
       <c r="Q306" s="1"/>
       <c r="R306" s="1"/>
       <c r="S306" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="T306" s="1" t="s">
         <v>29</v>
@@ -19200,22 +19228,22 @@
         <v>2</v>
       </c>
       <c r="D307" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E307" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="F307" s="1" t="n">
+        <v>124520438</v>
+      </c>
+      <c r="G307" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H307" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I307" s="2" t="s">
         <v>902</v>
-      </c>
-      <c r="F307" s="1" t="n">
-        <v>123219751</v>
-      </c>
-      <c r="G307" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H307" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I307" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="J307" s="2" t="s">
         <v>24</v>
@@ -19252,22 +19280,22 @@
         <v>2</v>
       </c>
       <c r="D308" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E308" s="1" t="s">
         <v>904</v>
       </c>
       <c r="F308" s="1" t="n">
-        <v>124192771</v>
+        <v>123219751</v>
       </c>
       <c r="G308" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H308" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I308" s="2" t="s">
-        <v>905</v>
+        <v>524</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>24</v>
@@ -19287,7 +19315,7 @@
       <c r="Q308" s="1"/>
       <c r="R308" s="1"/>
       <c r="S308" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="T308" s="1" t="s">
         <v>29</v>
@@ -19304,22 +19332,22 @@
         <v>2</v>
       </c>
       <c r="D309" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E309" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="F309" s="1" t="n">
+        <v>124192771</v>
+      </c>
+      <c r="G309" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H309" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I309" s="2" t="s">
         <v>907</v>
-      </c>
-      <c r="F309" s="1" t="n">
-        <v>123299304</v>
-      </c>
-      <c r="G309" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="H309" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I309" s="2" t="s">
-        <v>908</v>
       </c>
       <c r="J309" s="2" t="s">
         <v>24</v>
@@ -19339,7 +19367,7 @@
       <c r="Q309" s="1"/>
       <c r="R309" s="1"/>
       <c r="S309" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="T309" s="1" t="s">
         <v>29</v>
@@ -19356,22 +19384,22 @@
         <v>2</v>
       </c>
       <c r="D310" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E310" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="F310" s="1" t="n">
+        <v>123299304</v>
+      </c>
+      <c r="G310" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="H310" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I310" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="F310" s="1" t="n">
-        <v>122620357</v>
-      </c>
-      <c r="G310" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="H310" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I310" s="2" t="s">
-        <v>911</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>24</v>
@@ -19391,7 +19419,7 @@
       <c r="Q310" s="1"/>
       <c r="R310" s="1"/>
       <c r="S310" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="T310" s="1" t="s">
         <v>29</v>
@@ -19408,13 +19436,13 @@
         <v>2</v>
       </c>
       <c r="D311" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F311" s="1" t="n">
-        <v>123801078</v>
+        <v>122620357</v>
       </c>
       <c r="G311" s="1" t="n">
         <v>7</v>
@@ -19423,7 +19451,7 @@
         <v>22</v>
       </c>
       <c r="I311" s="2" t="s">
-        <v>537</v>
+        <v>913</v>
       </c>
       <c r="J311" s="2" t="s">
         <v>24</v>
@@ -19460,22 +19488,22 @@
         <v>2</v>
       </c>
       <c r="D312" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E312" s="1" t="s">
         <v>915</v>
       </c>
       <c r="F312" s="1" t="n">
-        <v>125532526</v>
+        <v>123801078</v>
       </c>
       <c r="G312" s="1" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H312" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I312" s="2" t="s">
-        <v>639</v>
+        <v>537</v>
       </c>
       <c r="J312" s="2" t="s">
         <v>24</v>
@@ -19512,22 +19540,22 @@
         <v>2</v>
       </c>
       <c r="D313" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E313" s="1" t="s">
         <v>917</v>
       </c>
       <c r="F313" s="1" t="n">
-        <v>123291202</v>
+        <v>125532526</v>
       </c>
       <c r="G313" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H313" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I313" s="2" t="s">
-        <v>882</v>
+        <v>639</v>
       </c>
       <c r="J313" s="2" t="s">
         <v>24</v>
@@ -19564,22 +19592,22 @@
         <v>2</v>
       </c>
       <c r="D314" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E314" s="1" t="s">
         <v>919</v>
       </c>
       <c r="F314" s="1" t="n">
-        <v>123222807</v>
+        <v>123291202</v>
       </c>
       <c r="G314" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H314" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I314" s="2" t="s">
-        <v>920</v>
+        <v>884</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>24</v>
@@ -19599,7 +19627,7 @@
       <c r="Q314" s="1"/>
       <c r="R314" s="1"/>
       <c r="S314" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="T314" s="1" t="s">
         <v>29</v>
@@ -19616,22 +19644,22 @@
         <v>2</v>
       </c>
       <c r="D315" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E315" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="F315" s="1" t="n">
+        <v>123222807</v>
+      </c>
+      <c r="G315" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I315" s="2" t="s">
         <v>922</v>
-      </c>
-      <c r="F315" s="1" t="n">
-        <v>123797661</v>
-      </c>
-      <c r="G315" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H315" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I315" s="2" t="s">
-        <v>616</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>24</v>
@@ -19651,7 +19679,7 @@
       <c r="Q315" s="1"/>
       <c r="R315" s="1"/>
       <c r="S315" s="1" t="s">
-        <v>181</v>
+        <v>923</v>
       </c>
       <c r="T315" s="1" t="s">
         <v>29</v>
@@ -19668,22 +19696,22 @@
         <v>2</v>
       </c>
       <c r="D316" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F316" s="1" t="n">
-        <v>123950750</v>
+        <v>123797661</v>
       </c>
       <c r="G316" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H316" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I316" s="2" t="s">
-        <v>924</v>
+        <v>616</v>
       </c>
       <c r="J316" s="2" t="s">
         <v>24</v>
@@ -19703,7 +19731,7 @@
       <c r="Q316" s="1"/>
       <c r="R316" s="1"/>
       <c r="S316" s="1" t="s">
-        <v>925</v>
+        <v>181</v>
       </c>
       <c r="T316" s="1" t="s">
         <v>29</v>
@@ -19720,25 +19748,25 @@
         <v>2</v>
       </c>
       <c r="D317" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E317" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="F317" s="1" t="n">
+        <v>123950750</v>
+      </c>
+      <c r="G317" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H317" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I317" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="F317" s="1" t="n">
-        <v>123898781</v>
-      </c>
-      <c r="G317" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H317" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I317" s="2" t="s">
-        <v>584</v>
-      </c>
       <c r="J317" s="2" t="s">
-        <v>426</v>
+        <v>24</v>
       </c>
       <c r="K317" s="2" t="s">
         <v>25</v>
@@ -19749,15 +19777,13 @@
       <c r="M317" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N317" s="1" t="s">
-        <v>927</v>
-      </c>
+      <c r="N317" s="1"/>
       <c r="O317" s="1"/>
       <c r="P317" s="1"/>
       <c r="Q317" s="1"/>
       <c r="R317" s="1"/>
       <c r="S317" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="T317" s="1" t="s">
         <v>29</v>
@@ -19774,42 +19800,44 @@
         <v>2</v>
       </c>
       <c r="D318" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E318" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="F318" s="1" t="n">
+        <v>123898781</v>
+      </c>
+      <c r="G318" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H318" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I318" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="J318" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K318" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L318" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M318" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N318" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="F318" s="1" t="n">
-        <v>124987550</v>
-      </c>
-      <c r="G318" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H318" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I318" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="J318" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K318" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L318" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M318" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N318" s="1"/>
       <c r="O318" s="1"/>
       <c r="P318" s="1"/>
       <c r="Q318" s="1"/>
       <c r="R318" s="1"/>
       <c r="S318" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="T318" s="1" t="s">
         <v>29</v>
@@ -19826,22 +19854,22 @@
         <v>2</v>
       </c>
       <c r="D319" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E319" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="F319" s="1" t="n">
+        <v>124987550</v>
+      </c>
+      <c r="G319" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H319" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I319" s="2" t="s">
         <v>932</v>
-      </c>
-      <c r="F319" s="1" t="n">
-        <v>123417846</v>
-      </c>
-      <c r="G319" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H319" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I319" s="2" t="s">
-        <v>756</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>24</v>
@@ -19878,25 +19906,25 @@
         <v>2</v>
       </c>
       <c r="D320" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>934</v>
       </c>
       <c r="F320" s="1" t="n">
-        <v>123302544</v>
+        <v>123417846</v>
       </c>
       <c r="G320" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H320" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I320" s="2" t="s">
-        <v>935</v>
+        <v>756</v>
       </c>
       <c r="J320" s="2" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="K320" s="2" t="s">
         <v>25</v>
@@ -19913,7 +19941,7 @@
       <c r="Q320" s="1"/>
       <c r="R320" s="1"/>
       <c r="S320" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="T320" s="1" t="s">
         <v>29</v>
@@ -19921,7 +19949,7 @@
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="n">
-        <v>300558959</v>
+        <v>300558944</v>
       </c>
       <c r="B321" s="1" t="s">
         <v>20</v>
@@ -19930,25 +19958,25 @@
         <v>2</v>
       </c>
       <c r="D321" s="1" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E321" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="F321" s="1" t="n">
+        <v>123302544</v>
+      </c>
+      <c r="G321" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I321" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="F321" s="1" t="n">
-        <v>124742108</v>
-      </c>
-      <c r="G321" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="H321" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I321" s="2" t="s">
-        <v>938</v>
-      </c>
       <c r="J321" s="2" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="K321" s="2" t="s">
         <v>25</v>
@@ -19965,7 +19993,7 @@
       <c r="Q321" s="1"/>
       <c r="R321" s="1"/>
       <c r="S321" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="T321" s="1" t="s">
         <v>29</v>
@@ -19982,22 +20010,22 @@
         <v>2</v>
       </c>
       <c r="D322" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E322" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="F322" s="1" t="n">
+        <v>124742108</v>
+      </c>
+      <c r="G322" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="H322" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I322" s="2" t="s">
         <v>940</v>
-      </c>
-      <c r="F322" s="1" t="n">
-        <v>122464777</v>
-      </c>
-      <c r="G322" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H322" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I322" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>24</v>
@@ -20034,22 +20062,22 @@
         <v>2</v>
       </c>
       <c r="D323" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E323" s="1" t="s">
         <v>942</v>
       </c>
       <c r="F323" s="1" t="n">
-        <v>123463213</v>
+        <v>122464777</v>
       </c>
       <c r="G323" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H323" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I323" s="2" t="s">
-        <v>943</v>
+        <v>793</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>24</v>
@@ -20069,7 +20097,7 @@
       <c r="Q323" s="1"/>
       <c r="R323" s="1"/>
       <c r="S323" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="T323" s="1" t="s">
         <v>29</v>
@@ -20086,22 +20114,22 @@
         <v>2</v>
       </c>
       <c r="D324" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E324" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="F324" s="1" t="n">
+        <v>123463213</v>
+      </c>
+      <c r="G324" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H324" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I324" s="2" t="s">
         <v>945</v>
-      </c>
-      <c r="F324" s="1" t="n">
-        <v>124323281</v>
-      </c>
-      <c r="G324" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H324" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I324" s="2" t="s">
-        <v>946</v>
       </c>
       <c r="J324" s="2" t="s">
         <v>24</v>
@@ -20121,7 +20149,7 @@
       <c r="Q324" s="1"/>
       <c r="R324" s="1"/>
       <c r="S324" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="T324" s="1" t="s">
         <v>29</v>
@@ -20138,22 +20166,22 @@
         <v>2</v>
       </c>
       <c r="D325" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E325" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="F325" s="1" t="n">
+        <v>124323281</v>
+      </c>
+      <c r="G325" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H325" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I325" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="F325" s="1" t="n">
-        <v>123585768</v>
-      </c>
-      <c r="G325" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H325" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I325" s="2" t="s">
-        <v>949</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>24</v>
@@ -20173,7 +20201,7 @@
       <c r="Q325" s="1"/>
       <c r="R325" s="1"/>
       <c r="S325" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="T325" s="1" t="s">
         <v>29</v>
@@ -20190,22 +20218,22 @@
         <v>2</v>
       </c>
       <c r="D326" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E326" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="F326" s="1" t="n">
+        <v>123585768</v>
+      </c>
+      <c r="G326" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H326" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I326" s="2" t="s">
         <v>951</v>
-      </c>
-      <c r="F326" s="1" t="n">
-        <v>124187802</v>
-      </c>
-      <c r="G326" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H326" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I326" s="2" t="s">
-        <v>952</v>
       </c>
       <c r="J326" s="2" t="s">
         <v>24</v>
@@ -20225,7 +20253,7 @@
       <c r="Q326" s="1"/>
       <c r="R326" s="1"/>
       <c r="S326" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="T326" s="1" t="s">
         <v>29</v>
@@ -20242,22 +20270,22 @@
         <v>2</v>
       </c>
       <c r="D327" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E327" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="F327" s="1" t="n">
+        <v>124187802</v>
+      </c>
+      <c r="G327" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H327" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I327" s="2" t="s">
         <v>954</v>
-      </c>
-      <c r="F327" s="1" t="n">
-        <v>124190462</v>
-      </c>
-      <c r="G327" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H327" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I327" s="2" t="s">
-        <v>955</v>
       </c>
       <c r="J327" s="2" t="s">
         <v>24</v>
@@ -20277,7 +20305,7 @@
       <c r="Q327" s="1"/>
       <c r="R327" s="1"/>
       <c r="S327" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="T327" s="1" t="s">
         <v>29</v>
@@ -20294,22 +20322,22 @@
         <v>2</v>
       </c>
       <c r="D328" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E328" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F328" s="1" t="n">
+        <v>124190462</v>
+      </c>
+      <c r="G328" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H328" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I328" s="2" t="s">
         <v>957</v>
-      </c>
-      <c r="F328" s="1" t="n">
-        <v>125531381</v>
-      </c>
-      <c r="G328" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H328" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I328" s="2" t="s">
-        <v>958</v>
       </c>
       <c r="J328" s="2" t="s">
         <v>24</v>
@@ -20329,7 +20357,7 @@
       <c r="Q328" s="1"/>
       <c r="R328" s="1"/>
       <c r="S328" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="T328" s="1" t="s">
         <v>29</v>
@@ -20346,22 +20374,22 @@
         <v>2</v>
       </c>
       <c r="D329" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E329" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="F329" s="1" t="n">
+        <v>125531381</v>
+      </c>
+      <c r="G329" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H329" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I329" s="2" t="s">
         <v>960</v>
-      </c>
-      <c r="F329" s="1" t="n">
-        <v>124490223</v>
-      </c>
-      <c r="G329" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H329" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I329" s="2" t="s">
-        <v>961</v>
       </c>
       <c r="J329" s="2" t="s">
         <v>24</v>
@@ -20381,7 +20409,7 @@
       <c r="Q329" s="1"/>
       <c r="R329" s="1"/>
       <c r="S329" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="T329" s="1" t="s">
         <v>29</v>
@@ -20398,22 +20426,22 @@
         <v>2</v>
       </c>
       <c r="D330" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E330" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="F330" s="1" t="n">
+        <v>124490223</v>
+      </c>
+      <c r="G330" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H330" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I330" s="2" t="s">
         <v>963</v>
-      </c>
-      <c r="F330" s="1" t="n">
-        <v>123861365</v>
-      </c>
-      <c r="G330" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H330" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I330" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="J330" s="2" t="s">
         <v>24</v>
@@ -20433,7 +20461,7 @@
       <c r="Q330" s="1"/>
       <c r="R330" s="1"/>
       <c r="S330" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="T330" s="1" t="s">
         <v>29</v>
@@ -20450,34 +20478,34 @@
         <v>2</v>
       </c>
       <c r="D331" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>498</v>
+        <v>965</v>
       </c>
       <c r="F331" s="1" t="n">
-        <v>122783116</v>
-      </c>
-      <c r="G331" s="1" t="s">
-        <v>38</v>
+        <v>123861365</v>
+      </c>
+      <c r="G331" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="H331" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>499</v>
+        <v>966</v>
       </c>
       <c r="J331" s="2" t="s">
-        <v>251</v>
+        <v>24</v>
       </c>
       <c r="K331" s="2" t="s">
-        <v>251</v>
+        <v>25</v>
       </c>
       <c r="L331" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="M331" s="2" t="s">
-        <v>251</v>
+        <v>26</v>
+      </c>
+      <c r="M331" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
@@ -20485,7 +20513,7 @@
       <c r="Q331" s="1"/>
       <c r="R331" s="1"/>
       <c r="S331" s="1" t="s">
-        <v>501</v>
+        <v>967</v>
       </c>
       <c r="T331" s="1" t="s">
         <v>29</v>
@@ -20502,7 +20530,7 @@
         <v>2</v>
       </c>
       <c r="D332" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>498</v>
@@ -20520,16 +20548,16 @@
         <v>499</v>
       </c>
       <c r="J332" s="2" t="s">
-        <v>750</v>
+        <v>251</v>
       </c>
       <c r="K332" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="L332" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M332" s="1" t="s">
-        <v>27</v>
+        <v>193</v>
+      </c>
+      <c r="M332" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
@@ -20554,25 +20582,25 @@
         <v>2</v>
       </c>
       <c r="D333" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>966</v>
+        <v>498</v>
       </c>
       <c r="F333" s="1" t="n">
-        <v>123255265</v>
-      </c>
-      <c r="G333" s="1" t="n">
-        <v>3</v>
+        <v>122783116</v>
+      </c>
+      <c r="G333" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="H333" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>967</v>
+        <v>499</v>
       </c>
       <c r="J333" s="2" t="s">
-        <v>24</v>
+        <v>750</v>
       </c>
       <c r="K333" s="2" t="s">
         <v>25</v>
@@ -20589,7 +20617,7 @@
       <c r="Q333" s="1"/>
       <c r="R333" s="1"/>
       <c r="S333" s="1" t="s">
-        <v>968</v>
+        <v>501</v>
       </c>
       <c r="T333" s="1" t="s">
         <v>29</v>
@@ -20606,22 +20634,22 @@
         <v>2</v>
       </c>
       <c r="D334" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E334" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="F334" s="1" t="n">
+        <v>123255265</v>
+      </c>
+      <c r="G334" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H334" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I334" s="2" t="s">
         <v>969</v>
-      </c>
-      <c r="F334" s="1" t="n">
-        <v>122794874</v>
-      </c>
-      <c r="G334" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H334" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I334" s="2" t="s">
-        <v>970</v>
       </c>
       <c r="J334" s="2" t="s">
         <v>24</v>
@@ -20641,7 +20669,7 @@
       <c r="Q334" s="1"/>
       <c r="R334" s="1"/>
       <c r="S334" s="1" t="s">
-        <v>772</v>
+        <v>970</v>
       </c>
       <c r="T334" s="1" t="s">
         <v>29</v>
@@ -20658,16 +20686,16 @@
         <v>2</v>
       </c>
       <c r="D335" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E335" s="1" t="s">
         <v>971</v>
       </c>
       <c r="F335" s="1" t="n">
-        <v>124196617</v>
+        <v>122794874</v>
       </c>
       <c r="G335" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H335" s="1" t="s">
         <v>22</v>
@@ -20679,23 +20707,21 @@
         <v>24</v>
       </c>
       <c r="K335" s="2" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="L335" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M335" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N335" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="M335" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N335" s="1"/>
       <c r="O335" s="1"/>
       <c r="P335" s="1"/>
       <c r="Q335" s="1"/>
       <c r="R335" s="1"/>
       <c r="S335" s="1" t="s">
-        <v>973</v>
+        <v>772</v>
       </c>
       <c r="T335" s="1" t="s">
         <v>29</v>
@@ -20712,36 +20738,38 @@
         <v>2</v>
       </c>
       <c r="D336" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E336" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="F336" s="1" t="n">
+        <v>124196617</v>
+      </c>
+      <c r="G336" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H336" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I336" s="2" t="s">
         <v>974</v>
       </c>
-      <c r="F336" s="1" t="n">
-        <v>124193372</v>
-      </c>
-      <c r="G336" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H336" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I336" s="2" t="s">
-        <v>897</v>
-      </c>
       <c r="J336" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K336" s="2" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="L336" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M336" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N336" s="1"/>
+        <v>51</v>
+      </c>
+      <c r="M336" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N336" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="O336" s="1"/>
       <c r="P336" s="1"/>
       <c r="Q336" s="1"/>
@@ -20764,34 +20792,34 @@
         <v>2</v>
       </c>
       <c r="D337" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>976</v>
       </c>
       <c r="F337" s="1" t="n">
-        <v>123557424</v>
+        <v>124193372</v>
       </c>
       <c r="G337" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H337" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I337" s="2" t="s">
-        <v>977</v>
+        <v>899</v>
       </c>
       <c r="J337" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K337" s="2" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="L337" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M337" s="2" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="M337" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
@@ -20799,7 +20827,7 @@
       <c r="Q337" s="1"/>
       <c r="R337" s="1"/>
       <c r="S337" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="T337" s="1" t="s">
         <v>29</v>
@@ -20816,44 +20844,42 @@
         <v>2</v>
       </c>
       <c r="D338" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E338" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="F338" s="1" t="n">
+        <v>123557424</v>
+      </c>
+      <c r="G338" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I338" s="2" t="s">
         <v>979</v>
       </c>
-      <c r="F338" s="1" t="n">
-        <v>123684162</v>
-      </c>
-      <c r="G338" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H338" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I338" s="2" t="s">
-        <v>980</v>
-      </c>
       <c r="J338" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K338" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="L338" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M338" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N338" s="1" t="s">
-        <v>85</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="M338" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N338" s="1"/>
       <c r="O338" s="1"/>
       <c r="P338" s="1"/>
       <c r="Q338" s="1"/>
       <c r="R338" s="1"/>
       <c r="S338" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="T338" s="1" t="s">
         <v>29</v>
@@ -20870,23 +20896,23 @@
         <v>2</v>
       </c>
       <c r="D339" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E339" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="F339" s="1" t="n">
+        <v>123684162</v>
+      </c>
+      <c r="G339" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H339" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I339" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="F339" s="1" t="n">
-        <v>124839614</v>
-      </c>
-      <c r="G339" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H339" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I339" s="2" t="s">
-        <v>983</v>
-      </c>
       <c r="J339" s="2" t="s">
         <v>24</v>
       </c>
@@ -20899,13 +20925,15 @@
       <c r="M339" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N339" s="1"/>
+      <c r="N339" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="O339" s="1"/>
       <c r="P339" s="1"/>
       <c r="Q339" s="1"/>
       <c r="R339" s="1"/>
       <c r="S339" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="T339" s="1" t="s">
         <v>29</v>
@@ -20922,22 +20950,22 @@
         <v>2</v>
       </c>
       <c r="D340" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E340" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="F340" s="1" t="n">
+        <v>124839614</v>
+      </c>
+      <c r="G340" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H340" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I340" s="2" t="s">
         <v>985</v>
-      </c>
-      <c r="F340" s="1" t="n">
-        <v>122830369</v>
-      </c>
-      <c r="G340" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H340" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I340" s="2" t="s">
-        <v>832</v>
       </c>
       <c r="J340" s="2" t="s">
         <v>24</v>
@@ -20957,7 +20985,7 @@
       <c r="Q340" s="1"/>
       <c r="R340" s="1"/>
       <c r="S340" s="1" t="s">
-        <v>889</v>
+        <v>986</v>
       </c>
       <c r="T340" s="1" t="s">
         <v>29</v>
@@ -20974,13 +21002,13 @@
         <v>2</v>
       </c>
       <c r="D341" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F341" s="1" t="n">
-        <v>122755270</v>
+        <v>122830369</v>
       </c>
       <c r="G341" s="1" t="n">
         <v>1</v>
@@ -20989,7 +21017,7 @@
         <v>22</v>
       </c>
       <c r="I341" s="2" t="s">
-        <v>651</v>
+        <v>832</v>
       </c>
       <c r="J341" s="2" t="s">
         <v>24</v>
@@ -21009,7 +21037,7 @@
       <c r="Q341" s="1"/>
       <c r="R341" s="1"/>
       <c r="S341" s="1" t="s">
-        <v>987</v>
+        <v>891</v>
       </c>
       <c r="T341" s="1" t="s">
         <v>29</v>
@@ -21026,22 +21054,22 @@
         <v>2</v>
       </c>
       <c r="D342" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>988</v>
       </c>
       <c r="F342" s="1" t="n">
-        <v>124052751</v>
+        <v>122755270</v>
       </c>
       <c r="G342" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>22</v>
       </c>
       <c r="I342" s="2" t="s">
-        <v>869</v>
+        <v>651</v>
       </c>
       <c r="J342" s="2" t="s">
         <v>24</v>
@@ -21064,6 +21092,58 @@
         <v>989</v>
       </c>
       <c r="T342" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A343" s="1" t="n">
+        <v>300558959</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C343" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D343" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="F343" s="1" t="n">
+        <v>124052751</v>
+      </c>
+      <c r="G343" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H343" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I343" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="J343" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K343" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L343" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M343" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N343" s="1"/>
+      <c r="O343" s="1"/>
+      <c r="P343" s="1"/>
+      <c r="Q343" s="1"/>
+      <c r="R343" s="1"/>
+      <c r="S343" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="T343" s="1" t="s">
         <v>29</v>
       </c>
     </row>
